--- a/clients/showroom-real/catalog.xlsx
+++ b/clients/showroom-real/catalog.xlsx
@@ -555,7 +555,7 @@
         <v/>
       </c>
       <c r="O3" t="str">
-        <v>/assets/showroom-real/sofa-cama-milano-01.jpg</v>
+        <v>assets/showroom-real/sofa-cama-milano-01.jpg</v>
       </c>
       <c r="P3" t="str">
         <v/>
